--- a/sample_data/wedstrijd-data-2026-09-26.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-26.xlsx
@@ -1288,10 +1288,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>264.068794</v>
+        <v>261.238509</v>
       </c>
       <c r="D12" t="n">
-        <v>188.36177</v>
+        <v>175.74635</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>245.430846</v>
+        <v>238.503543</v>
       </c>
       <c r="D19" t="n">
-        <v>196.10446</v>
+        <v>185.15575</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>314.868295</v>
+        <v>348.493237</v>
       </c>
       <c r="D20" t="n">
-        <v>241.483219</v>
+        <v>237.472569</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>277.574375</v>
+        <v>278.153709</v>
       </c>
       <c r="D26" t="n">
-        <v>210.159335</v>
+        <v>174.009244</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>

--- a/sample_data/wedstrijd-data-2026-09-26.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-26.xlsx
@@ -1078,10 +1078,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>257.109348</v>
+        <v>288.845564</v>
       </c>
       <c r="D2" t="n">
-        <v>151.768975</v>
+        <v>170.818167</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>196.87895</v>
+        <v>221.180646</v>
       </c>
       <c r="D3" t="n">
-        <v>116.424887</v>
+        <v>131.037888</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>431.239741</v>
+        <v>484.469691</v>
       </c>
       <c r="D4" t="n">
-        <v>132.949871</v>
+        <v>149.636995</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>111.018924</v>
+        <v>124.722512</v>
       </c>
       <c r="D5" t="n">
-        <v>319.075483</v>
+        <v>359.124052</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>65.32852800000001</v>
+        <v>73.392335</v>
       </c>
       <c r="D6" t="n">
-        <v>153.231019</v>
+        <v>172.463719</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>380.764562</v>
+        <v>427.764123</v>
       </c>
       <c r="D7" t="n">
-        <v>233.73211</v>
+        <v>263.068856</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>393.129322</v>
+        <v>441.655123</v>
       </c>
       <c r="D8" t="n">
-        <v>288.233137</v>
+        <v>324.410548</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>66.210802</v>
+        <v>74.38351299999999</v>
       </c>
       <c r="D9" t="n">
-        <v>250.253932</v>
+        <v>281.664405</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>224.231446</v>
+        <v>251.909388</v>
       </c>
       <c r="D10" t="n">
-        <v>159.781911</v>
+        <v>179.836843</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>466.519033</v>
+        <v>524.103673</v>
       </c>
       <c r="D11" t="n">
-        <v>210.796599</v>
+        <v>237.254608</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>261.238509</v>
+        <v>293.484407</v>
       </c>
       <c r="D12" t="n">
-        <v>175.74635</v>
+        <v>197.805048</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>485.764085</v>
+        <v>545.724232</v>
       </c>
       <c r="D13" t="n">
-        <v>309.771905</v>
+        <v>348.65274</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>155.250233</v>
+        <v>174.4135</v>
       </c>
       <c r="D14" t="n">
-        <v>269.177796</v>
+        <v>302.963486</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>65.780171</v>
+        <v>73.899727</v>
       </c>
       <c r="D15" t="n">
-        <v>188.263245</v>
+        <v>211.892993</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>185.113911</v>
+        <v>207.963392</v>
       </c>
       <c r="D16" t="n">
-        <v>319.030082</v>
+        <v>359.072952</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>333.65651</v>
+        <v>374.841303</v>
       </c>
       <c r="D17" t="n">
-        <v>339.268102</v>
+        <v>381.851136</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>175.626806</v>
+        <v>197.305249</v>
       </c>
       <c r="D18" t="n">
-        <v>242.966074</v>
+        <v>273.461816</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>238.503543</v>
+        <v>267.943157</v>
       </c>
       <c r="D19" t="n">
-        <v>185.15575</v>
+        <v>208.395463</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>348.493237</v>
+        <v>391.509397</v>
       </c>
       <c r="D20" t="n">
-        <v>237.472569</v>
+        <v>267.278797</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>399.902824</v>
+        <v>449.26471</v>
       </c>
       <c r="D21" t="n">
-        <v>328.053978</v>
+        <v>369.229478</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>333.482636</v>
+        <v>374.645967</v>
       </c>
       <c r="D22" t="n">
-        <v>126.406213</v>
+        <v>142.272013</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>358.462907</v>
+        <v>402.70967</v>
       </c>
       <c r="D23" t="n">
-        <v>118.222879</v>
+        <v>133.061553</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>330.885265</v>
+        <v>371.72799</v>
       </c>
       <c r="D24" t="n">
-        <v>150.221834</v>
+        <v>169.076838</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>424.538535</v>
+        <v>476.941324</v>
       </c>
       <c r="D25" t="n">
-        <v>337.421186</v>
+        <v>379.772405</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>278.153709</v>
+        <v>312.48753</v>
       </c>
       <c r="D26" t="n">
-        <v>174.009244</v>
+        <v>195.84991</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>422.850565</v>
+        <v>475.044999</v>
       </c>
       <c r="D27" t="n">
-        <v>204.822125</v>
+        <v>230.530252</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>86.389354</v>
+        <v>97.05279899999999</v>
       </c>
       <c r="D28" t="n">
-        <v>137.135352</v>
+        <v>154.347814</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>371.582555</v>
+        <v>417.448738</v>
       </c>
       <c r="D29" t="n">
-        <v>252.437509</v>
+        <v>284.122053</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>416.129747</v>
+        <v>467.4946</v>
       </c>
       <c r="D30" t="n">
-        <v>214.687296</v>
+        <v>241.633644</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>420.627829</v>
+        <v>472.547901</v>
       </c>
       <c r="D31" t="n">
-        <v>311.179874</v>
+        <v>350.237431</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>230.973689</v>
+        <v>259.483858</v>
       </c>
       <c r="D32" t="n">
-        <v>143.866063</v>
+        <v>161.923326</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>69.61526000000001</v>
+        <v>78.20819899999999</v>
       </c>
       <c r="D33" t="n">
-        <v>240.192599</v>
+        <v>270.34023</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>275.228415</v>
+        <v>309.201153</v>
       </c>
       <c r="D34" t="n">
-        <v>121.966716</v>
+        <v>137.275295</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
